--- a/data/fixtures/metadata/karakteristiske_brancher.xlsx
+++ b/data/fixtures/metadata/karakteristiske_brancher.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Z</t>
         </is>
       </c>
     </row>
